--- a/histograms/histogram_Rate__umol__g_h_.xlsx
+++ b/histograms/histogram_Rate__umol__g_h_.xlsx
@@ -442,111 +442,111 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>519750.00006435</v>
+        <v>3900.00975</v>
       </c>
       <c r="B2" t="n">
-        <v>26181</v>
+        <v>648</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1559250.00006105</v>
+        <v>11700.00925</v>
       </c>
       <c r="B3" t="n">
-        <v>127</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2598750.00005775</v>
+        <v>19500.00875</v>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3638250.00005445</v>
+        <v>27300.00825</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4677750.00005115</v>
+        <v>35100.00775</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5717250.000047849</v>
+        <v>42900.00725</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6756750.00004455</v>
+        <v>50700.00675</v>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7796250.00004125</v>
+        <v>58500.00625000001</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8835750.00003795</v>
+        <v>66300.00575</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9875250.000034649</v>
+        <v>74100.00524999999</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10914750.00003135</v>
+        <v>81900.00474999999</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11954250.00002805</v>
+        <v>89700.00425</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12993750.00002475</v>
+        <v>97500.00375</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14033250.00002145</v>
+        <v>105300.00325</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
@@ -554,50 +554,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15072750.00001815</v>
+        <v>113100.00275</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16112250.00001485</v>
+        <v>120900.00225</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17151750.00001155</v>
+        <v>128700.00175</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18191250.00000825</v>
+        <v>136500.00125</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19230750.00000495</v>
+        <v>144300.00075</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20270250.00000165</v>
+        <v>152100.00025</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
